--- a/Data/Metrics_Database.xlsx
+++ b/Data/Metrics_Database.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pablopadres/Documents/School/MS2/Thesis Prototype/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pablopadres/Documents/School/MS2/thesis/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4CF022C5-8AA1-5D41-BD84-9982181D84AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{073D52A6-3FD6-D549-A71C-B2BEC30C59E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="1320" windowWidth="27640" windowHeight="16940" xr2:uid="{C0BE3271-FB04-154D-AFA1-C88695D27245}"/>
+    <workbookView xWindow="13460" yWindow="1320" windowWidth="15680" windowHeight="16940" xr2:uid="{C0BE3271-FB04-154D-AFA1-C88695D27245}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,29 +36,20 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>Brand</t>
   </si>
   <si>
-    <t xml:space="preserve">Supply Chain Transparency </t>
-  </si>
-  <si>
     <t>Labor Conditions &amp; Wages</t>
   </si>
   <si>
     <t>Environmental Impact</t>
   </si>
   <si>
-    <t>Business Model Standards</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pricing v. Wage Equity </t>
   </si>
   <si>
-    <t>Controversy &amp; Violations</t>
-  </si>
-  <si>
     <t xml:space="preserve">GAP </t>
   </si>
   <si>
@@ -95,24 +86,9 @@
     <t>Wrangler</t>
   </si>
   <si>
-    <t>Lee</t>
-  </si>
-  <si>
-    <t>Carhartt</t>
-  </si>
-  <si>
-    <t>Dickies</t>
-  </si>
-  <si>
-    <t>Ralph Lauren</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tommy Hilfiger </t>
   </si>
   <si>
-    <t>Clavin Klein</t>
-  </si>
-  <si>
     <t>Michael Kors</t>
   </si>
   <si>
@@ -128,9 +104,6 @@
     <t>Victoria's Secret</t>
   </si>
   <si>
-    <t>SKIMS</t>
-  </si>
-  <si>
     <t>Forever 21</t>
   </si>
   <si>
@@ -149,9 +122,6 @@
     <t xml:space="preserve">Tom Ford </t>
   </si>
   <si>
-    <t>The Row</t>
-  </si>
-  <si>
     <t>Urban Outfitters</t>
   </si>
   <si>
@@ -165,6 +135,27 @@
   </si>
   <si>
     <t>CONTROL DATABASE</t>
+  </si>
+  <si>
+    <t>Kate Spade &amp; Co</t>
+  </si>
+  <si>
+    <t>The North Face</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Social Transparency </t>
+  </si>
+  <si>
+    <t>Human Rights Risk &amp; Responsiveness</t>
+  </si>
+  <si>
+    <t>Supply Chain Transparency</t>
+  </si>
+  <si>
+    <t>Ralph Lauren Corporation</t>
+  </si>
+  <si>
+    <t>Calvin Klein</t>
   </si>
 </sst>
 </file>
@@ -223,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -234,7 +225,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -569,15 +559,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1F81AE2-6F47-F043-A386-E3BDBE7802FE}">
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.83203125" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" customWidth="1"/>
+    <col min="7" max="7" width="15.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="C1" s="1"/>
       <c r="E1" s="1"/>
@@ -587,29 +578,29 @@
         <v>0</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G3" s="3" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="6">
+        <v>4</v>
+      </c>
+      <c r="B4" s="4">
         <v>48</v>
       </c>
       <c r="C4" s="4">
@@ -630,9 +621,9 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="6">
+        <v>5</v>
+      </c>
+      <c r="B5" s="4">
         <v>48</v>
       </c>
       <c r="C5" s="4">
@@ -653,9 +644,9 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="6">
+        <v>6</v>
+      </c>
+      <c r="B6" s="4">
         <v>48</v>
       </c>
       <c r="C6" s="4">
@@ -676,9 +667,9 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="6">
+        <v>7</v>
+      </c>
+      <c r="B7" s="4">
         <v>21</v>
       </c>
       <c r="C7" s="4">
@@ -699,9 +690,9 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="6">
+        <v>8</v>
+      </c>
+      <c r="B8" s="4">
         <v>33</v>
       </c>
       <c r="C8" s="4">
@@ -722,9 +713,9 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="6">
+        <v>9</v>
+      </c>
+      <c r="B9" s="4">
         <v>50</v>
       </c>
       <c r="C9" s="4">
@@ -745,9 +736,9 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="6">
+        <v>10</v>
+      </c>
+      <c r="B10" s="4">
         <v>28</v>
       </c>
       <c r="C10" s="4">
@@ -768,9 +759,9 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="6">
+        <v>11</v>
+      </c>
+      <c r="B11" s="4">
         <v>61</v>
       </c>
       <c r="C11" s="4">
@@ -791,9 +782,9 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="6">
+        <v>12</v>
+      </c>
+      <c r="B12" s="4">
         <v>46</v>
       </c>
       <c r="C12" s="4">
@@ -814,9 +805,9 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="6">
+        <v>13</v>
+      </c>
+      <c r="B13" s="4">
         <v>38</v>
       </c>
       <c r="C13" s="4">
@@ -837,9 +828,9 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="6">
+        <v>14</v>
+      </c>
+      <c r="B14" s="4">
         <v>60</v>
       </c>
       <c r="C14" s="4">
@@ -860,9 +851,9 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="6">
+        <v>15</v>
+      </c>
+      <c r="B15" s="4">
         <v>33</v>
       </c>
       <c r="C15" s="4">
@@ -883,68 +874,68 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" s="6">
-        <v>52</v>
+        <v>38</v>
+      </c>
+      <c r="B16" s="4">
+        <v>54</v>
       </c>
       <c r="C16" s="4">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" s="4">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E16" s="4">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F16" s="5">
-        <v>97.637308712878479</v>
+        <v>93.093671622260189</v>
       </c>
       <c r="G16" s="4">
-        <v>100</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="6">
-        <v>7</v>
+        <v>16</v>
+      </c>
+      <c r="B17" s="4">
+        <v>50</v>
       </c>
       <c r="C17" s="4">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D17" s="4">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E17" s="4">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="F17" s="5">
-        <v>96.202558837816696</v>
+        <v>94.470149548499492</v>
       </c>
       <c r="G17" s="4">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" s="6">
-        <v>49</v>
+        <v>39</v>
+      </c>
+      <c r="B18" s="4">
+        <v>48</v>
       </c>
       <c r="C18" s="4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D18" s="4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E18" s="4">
         <v>69</v>
       </c>
       <c r="F18" s="5">
-        <v>98.801172771792494</v>
+        <v>94.911126458507511</v>
       </c>
       <c r="G18" s="4">
         <v>100</v>
@@ -952,148 +943,148 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" s="6">
-        <v>54</v>
+        <v>17</v>
+      </c>
+      <c r="B19" s="4">
+        <v>23</v>
       </c>
       <c r="C19" s="4">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D19" s="4">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E19" s="4">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="F19" s="5">
-        <v>93.093671622260189</v>
+        <v>88.406717035889287</v>
       </c>
       <c r="G19" s="4">
-        <v>65</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20" s="6">
-        <v>50</v>
+        <v>18</v>
+      </c>
+      <c r="B20" s="4">
+        <v>42</v>
       </c>
       <c r="C20" s="4">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D20" s="4">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E20" s="4">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="F20" s="5">
-        <v>94.470149548499492</v>
+        <v>85.823852277270902</v>
       </c>
       <c r="G20" s="4">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21" s="6">
-        <v>48</v>
+        <v>33</v>
+      </c>
+      <c r="B21" s="4">
+        <v>50</v>
       </c>
       <c r="C21" s="4">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D21" s="4">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E21" s="4">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F21" s="5">
-        <v>94.911126458507511</v>
+        <v>74</v>
       </c>
       <c r="G21" s="4">
-        <v>100</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22" s="6">
-        <v>23</v>
+        <v>19</v>
+      </c>
+      <c r="B22" s="4">
+        <v>50</v>
       </c>
       <c r="C22" s="4">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D22" s="4">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E22" s="4">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="F22" s="5">
-        <v>88.406717035889287</v>
+        <v>95.955640732212856</v>
       </c>
       <c r="G22" s="4">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B23" s="6">
-        <v>42</v>
+        <v>20</v>
+      </c>
+      <c r="B23" s="4">
+        <v>38</v>
       </c>
       <c r="C23" s="4">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D23" s="4">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E23" s="4">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="F23" s="5">
-        <v>85.823852277270902</v>
+        <v>99.000399840063977</v>
       </c>
       <c r="G23" s="4">
-        <v>100</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B24" s="6">
-        <v>50</v>
+        <v>21</v>
+      </c>
+      <c r="B24" s="4">
+        <v>19</v>
       </c>
       <c r="C24" s="4">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="D24" s="4">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="E24" s="4">
         <v>60</v>
       </c>
       <c r="F24" s="5">
-        <v>95.955640732212856</v>
+        <v>93.414398946303834</v>
       </c>
       <c r="G24" s="4">
-        <v>90</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B25" s="6">
-        <v>38</v>
+        <v>34</v>
+      </c>
+      <c r="B25" s="4">
+        <v>19</v>
       </c>
       <c r="C25" s="4">
         <v>21</v>
@@ -1105,7 +1096,7 @@
         <v>60</v>
       </c>
       <c r="F25" s="5">
-        <v>99.000399840063977</v>
+        <v>93.414398946303834</v>
       </c>
       <c r="G25" s="4">
         <v>65</v>
@@ -1113,45 +1104,45 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B26" s="6">
-        <v>19</v>
+        <v>22</v>
+      </c>
+      <c r="B26" s="4">
+        <v>0</v>
       </c>
       <c r="C26" s="4">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D26" s="4">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E26" s="4">
-        <v>60</v>
+        <v>21.5</v>
       </c>
       <c r="F26" s="5">
-        <v>93.414398946303834</v>
+        <v>95.113065884757205</v>
       </c>
       <c r="G26" s="4">
-        <v>65</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B27" s="6">
-        <v>68</v>
+        <v>23</v>
+      </c>
+      <c r="B27" s="4">
+        <v>1</v>
       </c>
       <c r="C27" s="4">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="D27" s="4">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="E27" s="4">
         <v>75</v>
       </c>
       <c r="F27" s="5">
-        <v>92.238398758143802</v>
+        <v>85.328825668176307</v>
       </c>
       <c r="G27" s="4">
         <v>100</v>
@@ -1159,68 +1150,68 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B28" s="6">
-        <v>0</v>
+        <v>24</v>
+      </c>
+      <c r="B28" s="4">
+        <v>34</v>
       </c>
       <c r="C28" s="4">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="D28" s="4">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="E28" s="4">
-        <v>21.5</v>
+        <v>69</v>
       </c>
       <c r="F28" s="5">
-        <v>95.113065884757205</v>
+        <v>100</v>
       </c>
       <c r="G28" s="4">
-        <v>15</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B29" s="6">
-        <v>1</v>
+        <v>25</v>
+      </c>
+      <c r="B29" s="4">
+        <v>40</v>
       </c>
       <c r="C29" s="4">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="D29" s="4">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="E29" s="4">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="F29" s="5">
-        <v>85.328825668176307</v>
+        <v>93.603944903840883</v>
       </c>
       <c r="G29" s="4">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" s="4">
+        <v>28</v>
+      </c>
+      <c r="C30" s="4">
         <v>33</v>
       </c>
-      <c r="B30" s="6">
-        <v>34</v>
-      </c>
-      <c r="C30" s="4">
-        <v>47</v>
-      </c>
       <c r="D30" s="4">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="E30" s="4">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F30" s="5">
-        <v>100</v>
+        <v>78.012261299986079</v>
       </c>
       <c r="G30" s="4">
         <v>100</v>
@@ -1228,91 +1219,91 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B31" s="6">
-        <v>40</v>
+        <v>27</v>
+      </c>
+      <c r="B31" s="4">
+        <v>0</v>
       </c>
       <c r="C31" s="4">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="D31" s="4">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="E31" s="4">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F31" s="5">
-        <v>93.603944903840883</v>
+        <v>39.004892191367937</v>
       </c>
       <c r="G31" s="4">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B32" s="6">
         <v>28</v>
       </c>
+      <c r="B32" s="4">
+        <v>13</v>
+      </c>
       <c r="C32" s="4">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D32" s="4">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E32" s="4">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="F32" s="5">
-        <v>78.012261299986079</v>
+        <v>84.006397441023594</v>
       </c>
       <c r="G32" s="4">
-        <v>100</v>
+        <v>65</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B33" s="6">
-        <v>0</v>
+        <v>29</v>
+      </c>
+      <c r="B33" s="4">
+        <v>13</v>
       </c>
       <c r="C33" s="4">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D33" s="4">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E33" s="4">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="F33" s="5">
-        <v>39.004892191367937</v>
+        <v>87.534398005503675</v>
       </c>
       <c r="G33" s="4">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B34" s="6">
-        <v>46</v>
+        <v>30</v>
+      </c>
+      <c r="B34" s="4">
+        <v>13</v>
       </c>
       <c r="C34" s="4">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D34" s="4">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E34" s="4">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="F34" s="5">
-        <v>8.7871223422411049E-3</v>
+        <v>95.336354193158087</v>
       </c>
       <c r="G34" s="4">
         <v>100</v>
@@ -1320,93 +1311,24 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B35" s="6">
-        <v>13</v>
+        <v>31</v>
+      </c>
+      <c r="B35" s="4">
+        <v>8</v>
       </c>
       <c r="C35" s="4">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D35" s="4">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E35" s="4">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="F35" s="5">
-        <v>84.006397441023594</v>
+        <v>95.336354193158087</v>
       </c>
       <c r="G35" s="4">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A36" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B36" s="6">
-        <v>13</v>
-      </c>
-      <c r="C36" s="4">
-        <v>18</v>
-      </c>
-      <c r="D36" s="4">
-        <v>18</v>
-      </c>
-      <c r="E36" s="4">
-        <v>60</v>
-      </c>
-      <c r="F36" s="5">
-        <v>87.534398005503675</v>
-      </c>
-      <c r="G36" s="4">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A37" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B37" s="6">
-        <v>13</v>
-      </c>
-      <c r="C37" s="4">
-        <v>42</v>
-      </c>
-      <c r="D37" s="4">
-        <v>42</v>
-      </c>
-      <c r="E37" s="4">
-        <v>61</v>
-      </c>
-      <c r="F37" s="5">
-        <v>95.336354193158087</v>
-      </c>
-      <c r="G37" s="4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A38" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B38" s="6">
-        <v>8</v>
-      </c>
-      <c r="C38" s="4">
-        <v>23</v>
-      </c>
-      <c r="D38" s="4">
-        <v>23</v>
-      </c>
-      <c r="E38" s="4">
-        <v>69</v>
-      </c>
-      <c r="F38" s="5">
-        <v>95.336354193158087</v>
-      </c>
-      <c r="G38" s="4">
         <v>100</v>
       </c>
     </row>

--- a/Data/Metrics_Database.xlsx
+++ b/Data/Metrics_Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pablopadres/Documents/School/MS2/thesis/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{06CB09E5-E51E-854E-B0BD-C89A63B64B84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DB9D9DB-F4E0-9545-A4E0-D31B956015E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="Ethical Metrics Database" sheetId="3" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -81,9 +80,6 @@
     <t xml:space="preserve">Tommy Hilfiger </t>
   </si>
   <si>
-    <t xml:space="preserve">Clavin Klein </t>
-  </si>
-  <si>
     <t xml:space="preserve">Michael Kors </t>
   </si>
   <si>
@@ -99,9 +95,6 @@
     <t xml:space="preserve">Hanes </t>
   </si>
   <si>
-    <t>Victoria's Secret &amp; Co</t>
-  </si>
-  <si>
     <t>The North Face</t>
   </si>
   <si>
@@ -151,6 +144,12 @@
   </si>
   <si>
     <t>Value Distribution Equity</t>
+  </si>
+  <si>
+    <t>Victoria's Secret</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calvin Klein </t>
   </si>
 </sst>
 </file>
@@ -218,7 +217,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -233,9 +232,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -254,10 +250,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -477,24 +469,24 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I1" s="8"/>
+      <c r="I1" s="1"/>
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
@@ -517,7 +509,7 @@
       <c r="B2" s="3">
         <v>48</v>
       </c>
-      <c r="C2" s="9">
+      <c r="C2" s="8">
         <v>34</v>
       </c>
       <c r="D2" s="5">
@@ -529,7 +521,7 @@
       <c r="F2" s="6">
         <v>75</v>
       </c>
-      <c r="G2" s="9">
+      <c r="G2" s="8">
         <v>34</v>
       </c>
       <c r="J2" s="4"/>
@@ -541,7 +533,7 @@
       <c r="B3" s="3">
         <v>48</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="9">
         <v>34</v>
       </c>
       <c r="D3" s="5">
@@ -553,7 +545,7 @@
       <c r="F3" s="6">
         <v>75</v>
       </c>
-      <c r="G3" s="10">
+      <c r="G3" s="9">
         <v>34</v>
       </c>
     </row>
@@ -564,7 +556,7 @@
       <c r="B4" s="3">
         <v>48</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="9">
         <v>34</v>
       </c>
       <c r="D4" s="5">
@@ -576,7 +568,7 @@
       <c r="F4" s="6">
         <v>75</v>
       </c>
-      <c r="G4" s="10">
+      <c r="G4" s="9">
         <v>34</v>
       </c>
     </row>
@@ -587,7 +579,7 @@
       <c r="B5" s="3">
         <v>21</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="8">
         <v>47</v>
       </c>
       <c r="D5" s="5">
@@ -599,7 +591,7 @@
       <c r="F5" s="6">
         <v>0</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="8">
         <v>47</v>
       </c>
     </row>
@@ -610,7 +602,7 @@
       <c r="B6" s="3">
         <v>33</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="8">
         <v>52</v>
       </c>
       <c r="D6" s="5">
@@ -622,7 +614,7 @@
       <c r="F6" s="6">
         <v>75</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="8">
         <v>52</v>
       </c>
     </row>
@@ -633,7 +625,7 @@
       <c r="B7" s="3">
         <v>50</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="8">
         <v>34</v>
       </c>
       <c r="D7" s="5">
@@ -645,7 +637,7 @@
       <c r="F7" s="6">
         <v>75</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="8">
         <v>34</v>
       </c>
     </row>
@@ -656,7 +648,7 @@
       <c r="B8" s="3">
         <v>28</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="8">
         <v>20</v>
       </c>
       <c r="D8" s="5">
@@ -668,7 +660,7 @@
       <c r="F8" s="6">
         <v>50</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="8">
         <v>20</v>
       </c>
       <c r="J8" s="7"/>
@@ -677,10 +669,10 @@
       <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="10">
         <v>47</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="8">
         <v>63</v>
       </c>
       <c r="D9" s="5">
@@ -692,7 +684,7 @@
       <c r="F9" s="6">
         <v>75</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="8">
         <v>63</v>
       </c>
       <c r="J9" s="7"/>
@@ -704,7 +696,7 @@
       <c r="B10" s="3">
         <v>46</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="8">
         <v>54</v>
       </c>
       <c r="D10" s="5">
@@ -716,7 +708,7 @@
       <c r="F10" s="6">
         <v>75</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G10" s="8">
         <v>54</v>
       </c>
       <c r="J10" s="7"/>
@@ -725,10 +717,10 @@
       <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="9">
-        <v>0</v>
-      </c>
-      <c r="C11" s="9">
+      <c r="B11" s="8">
+        <v>0</v>
+      </c>
+      <c r="C11" s="8">
         <v>0</v>
       </c>
       <c r="D11" s="5">
@@ -740,7 +732,7 @@
       <c r="F11" s="6">
         <v>0</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G11" s="8">
         <v>0</v>
       </c>
       <c r="J11" s="7"/>
@@ -752,7 +744,7 @@
       <c r="B12" s="3">
         <v>60</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="8">
         <v>71</v>
       </c>
       <c r="D12" s="5">
@@ -764,7 +756,7 @@
       <c r="F12" s="6">
         <v>50</v>
       </c>
-      <c r="G12" s="9">
+      <c r="G12" s="8">
         <v>71</v>
       </c>
       <c r="J12" s="7"/>
@@ -776,7 +768,7 @@
       <c r="B13" s="3">
         <v>33</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C13" s="8">
         <v>28</v>
       </c>
       <c r="D13" s="5">
@@ -788,7 +780,7 @@
       <c r="F13" s="6">
         <v>75</v>
       </c>
-      <c r="G13" s="9">
+      <c r="G13" s="8">
         <v>28</v>
       </c>
       <c r="J13" s="7"/>
@@ -800,7 +792,7 @@
       <c r="B14" s="3">
         <v>54</v>
       </c>
-      <c r="C14" s="10">
+      <c r="C14" s="9">
         <v>40</v>
       </c>
       <c r="D14" s="5">
@@ -812,7 +804,7 @@
       <c r="F14" s="6">
         <v>75</v>
       </c>
-      <c r="G14" s="10">
+      <c r="G14" s="9">
         <v>40</v>
       </c>
       <c r="J14" s="7"/>
@@ -824,7 +816,7 @@
       <c r="B15" s="3">
         <v>50</v>
       </c>
-      <c r="C15" s="10">
+      <c r="C15" s="9">
         <v>77</v>
       </c>
       <c r="D15" s="5">
@@ -836,18 +828,18 @@
       <c r="F15" s="6">
         <v>75</v>
       </c>
-      <c r="G15" s="10">
+      <c r="G15" s="9">
         <v>77</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="3" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="B16" s="3">
         <v>48</v>
       </c>
-      <c r="C16" s="10">
+      <c r="C16" s="9">
         <v>61</v>
       </c>
       <c r="D16" s="5">
@@ -859,18 +851,18 @@
       <c r="F16" s="6">
         <v>75</v>
       </c>
-      <c r="G16" s="10">
+      <c r="G16" s="9">
         <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="3">
         <v>23</v>
       </c>
-      <c r="C17" s="10">
+      <c r="C17" s="9">
         <v>19</v>
       </c>
       <c r="D17" s="5">
@@ -882,18 +874,18 @@
       <c r="F17" s="6">
         <v>25</v>
       </c>
-      <c r="G17" s="10">
+      <c r="G17" s="9">
         <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="3">
         <v>42</v>
       </c>
-      <c r="C18" s="10">
+      <c r="C18" s="9">
         <v>33</v>
       </c>
       <c r="D18" s="5">
@@ -905,18 +897,18 @@
       <c r="F18" s="6">
         <v>50</v>
       </c>
-      <c r="G18" s="10">
+      <c r="G18" s="9">
         <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="3">
         <v>42</v>
       </c>
-      <c r="C19" s="10">
+      <c r="C19" s="9">
         <v>26</v>
       </c>
       <c r="D19" s="5">
@@ -928,18 +920,18 @@
       <c r="F19" s="6">
         <v>50</v>
       </c>
-      <c r="G19" s="10">
+      <c r="G19" s="9">
         <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="3">
         <v>50</v>
       </c>
-      <c r="C20" s="10">
+      <c r="C20" s="9">
         <v>31</v>
       </c>
       <c r="D20" s="5">
@@ -951,18 +943,18 @@
       <c r="F20" s="6">
         <v>75</v>
       </c>
-      <c r="G20" s="10">
+      <c r="G20" s="9">
         <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" s="3">
         <v>38</v>
       </c>
-      <c r="C21" s="10">
+      <c r="C21" s="9">
         <v>44</v>
       </c>
       <c r="D21" s="5">
@@ -974,18 +966,18 @@
       <c r="F21" s="6">
         <v>50</v>
       </c>
-      <c r="G21" s="10">
+      <c r="G21" s="9">
         <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="3" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="B22" s="3">
         <v>19</v>
       </c>
-      <c r="C22" s="10">
+      <c r="C22" s="9">
         <v>54</v>
       </c>
       <c r="D22" s="5">
@@ -997,18 +989,18 @@
       <c r="F22" s="6">
         <v>50</v>
       </c>
-      <c r="G22" s="10">
+      <c r="G22" s="9">
         <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B23" s="3">
         <v>66</v>
       </c>
-      <c r="C23" s="10">
+      <c r="C23" s="9">
         <v>58</v>
       </c>
       <c r="D23" s="5">
@@ -1020,18 +1012,18 @@
       <c r="F23" s="6">
         <v>75</v>
       </c>
-      <c r="G23" s="10">
+      <c r="G23" s="9">
         <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B24" s="11">
-        <v>0</v>
-      </c>
-      <c r="C24" s="10">
+        <v>21</v>
+      </c>
+      <c r="B24" s="10">
+        <v>0</v>
+      </c>
+      <c r="C24" s="9">
         <v>0</v>
       </c>
       <c r="D24" s="5">
@@ -1043,18 +1035,18 @@
       <c r="F24" s="6">
         <v>0</v>
       </c>
-      <c r="G24" s="10">
+      <c r="G24" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B25" s="3">
         <v>1</v>
       </c>
-      <c r="C25" s="10">
+      <c r="C25" s="9">
         <v>3</v>
       </c>
       <c r="D25" s="5">
@@ -1066,18 +1058,18 @@
       <c r="F25" s="6">
         <v>0</v>
       </c>
-      <c r="G25" s="10">
+      <c r="G25" s="9">
         <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B26" s="3">
         <v>34</v>
       </c>
-      <c r="C26" s="10">
+      <c r="C26" s="9">
         <v>41</v>
       </c>
       <c r="D26" s="5">
@@ -1089,41 +1081,41 @@
       <c r="F26" s="6">
         <v>75</v>
       </c>
-      <c r="G26" s="10">
+      <c r="G26" s="9">
         <v>41</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B27" s="3">
         <v>40</v>
       </c>
-      <c r="C27" s="10">
+      <c r="C27" s="9">
         <v>38</v>
       </c>
       <c r="D27" s="5">
         <v>3.1144660000000002</v>
       </c>
-      <c r="E27" s="11">
+      <c r="E27" s="10">
         <v>67</v>
       </c>
       <c r="F27" s="6">
         <v>50</v>
       </c>
-      <c r="G27" s="10">
+      <c r="G27" s="9">
         <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B28" s="3">
         <v>28</v>
       </c>
-      <c r="C28" s="10">
+      <c r="C28" s="9">
         <v>29</v>
       </c>
       <c r="D28" s="5">
@@ -1135,41 +1127,41 @@
       <c r="F28" s="6">
         <v>0</v>
       </c>
-      <c r="G28" s="10">
+      <c r="G28" s="9">
         <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B29" s="3">
         <v>0</v>
       </c>
-      <c r="C29" s="10">
+      <c r="C29" s="9">
         <v>0</v>
       </c>
       <c r="D29" s="5">
         <v>9.3811470000000003</v>
       </c>
-      <c r="E29" s="11">
+      <c r="E29" s="10">
         <v>4</v>
       </c>
       <c r="F29" s="6">
         <v>0</v>
       </c>
-      <c r="G29" s="10">
+      <c r="G29" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B30" s="3">
         <v>13</v>
       </c>
-      <c r="C30" s="10">
+      <c r="C30" s="9">
         <v>7</v>
       </c>
       <c r="D30" s="5">
@@ -1181,18 +1173,18 @@
       <c r="F30" s="6">
         <v>0</v>
       </c>
-      <c r="G30" s="10">
+      <c r="G30" s="9">
         <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B31" s="3">
         <v>13</v>
       </c>
-      <c r="C31" s="10">
+      <c r="C31" s="9">
         <v>7</v>
       </c>
       <c r="D31" s="5">
@@ -1204,18 +1196,18 @@
       <c r="F31" s="6">
         <v>0</v>
       </c>
-      <c r="G31" s="10">
+      <c r="G31" s="9">
         <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B32" s="3">
         <v>13</v>
       </c>
-      <c r="C32" s="10">
+      <c r="C32" s="9">
         <v>7</v>
       </c>
       <c r="D32" s="5">
@@ -1227,18 +1219,18 @@
       <c r="F32" s="6">
         <v>0</v>
       </c>
-      <c r="G32" s="10">
+      <c r="G32" s="9">
         <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B33" s="3">
         <v>8</v>
       </c>
-      <c r="C33" s="10">
+      <c r="C33" s="9">
         <v>9</v>
       </c>
       <c r="D33" s="5">
@@ -1250,7 +1242,7 @@
       <c r="F33" s="6">
         <v>0</v>
       </c>
-      <c r="G33" s="10">
+      <c r="G33" s="9">
         <v>9</v>
       </c>
     </row>

--- a/Data/Metrics_Database.xlsx
+++ b/Data/Metrics_Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pablopadres/Documents/School/MS2/thesis/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DB9D9DB-F4E0-9545-A4E0-D31B956015E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24873022-9693-DA4D-9BB0-0D50950B494E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>Brand</t>
   </si>
@@ -59,9 +59,6 @@
     <t>Under Armour</t>
   </si>
   <si>
-    <t>Lululemon</t>
-  </si>
-  <si>
     <t>New Balance</t>
   </si>
   <si>
@@ -74,9 +71,6 @@
     <t xml:space="preserve">Wrangler </t>
   </si>
   <si>
-    <t>Ralph Lauren Corporation</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tommy Hilfiger </t>
   </si>
   <si>
@@ -86,9 +80,6 @@
     <t>COACH</t>
   </si>
   <si>
-    <t>Kate Spade &amp; Co</t>
-  </si>
-  <si>
     <t xml:space="preserve">Converse </t>
   </si>
   <si>
@@ -143,13 +134,16 @@
     <t>Supply Chain Transparency</t>
   </si>
   <si>
-    <t>Value Distribution Equity</t>
-  </si>
-  <si>
     <t>Victoria's Secret</t>
   </si>
   <si>
     <t xml:space="preserve">Calvin Klein </t>
+  </si>
+  <si>
+    <t>Ralph Lauren</t>
+  </si>
+  <si>
+    <t>Kate Spade &amp; Co.</t>
   </si>
 </sst>
 </file>
@@ -453,7 +447,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z33"/>
+  <dimension ref="A1:Z32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="24.6640625" customWidth="1"/>
@@ -469,23 +463,21 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="G1" s="1"/>
       <c r="I1" s="1"/>
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
@@ -521,9 +513,7 @@
       <c r="F2" s="6">
         <v>75</v>
       </c>
-      <c r="G2" s="8">
-        <v>34</v>
-      </c>
+      <c r="G2" s="3"/>
       <c r="J2" s="4"/>
     </row>
     <row r="3" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -545,9 +535,6 @@
       <c r="F3" s="6">
         <v>75</v>
       </c>
-      <c r="G3" s="9">
-        <v>34</v>
-      </c>
     </row>
     <row r="4" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="3" t="s">
@@ -568,9 +555,6 @@
       <c r="F4" s="6">
         <v>75</v>
       </c>
-      <c r="G4" s="9">
-        <v>34</v>
-      </c>
     </row>
     <row r="5" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="3" t="s">
@@ -591,9 +575,7 @@
       <c r="F5" s="6">
         <v>0</v>
       </c>
-      <c r="G5" s="8">
-        <v>47</v>
-      </c>
+      <c r="G5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="3" t="s">
@@ -614,9 +596,7 @@
       <c r="F6" s="6">
         <v>75</v>
       </c>
-      <c r="G6" s="8">
-        <v>52</v>
-      </c>
+      <c r="G6" s="3"/>
     </row>
     <row r="7" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="3" t="s">
@@ -637,9 +617,7 @@
       <c r="F7" s="6">
         <v>75</v>
       </c>
-      <c r="G7" s="8">
-        <v>34</v>
-      </c>
+      <c r="G7" s="3"/>
     </row>
     <row r="8" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="3" t="s">
@@ -660,81 +638,73 @@
       <c r="F8" s="6">
         <v>50</v>
       </c>
-      <c r="G8" s="8">
-        <v>20</v>
-      </c>
+      <c r="G8" s="3"/>
       <c r="J8" s="7"/>
     </row>
     <row r="9" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="10">
-        <v>47</v>
+      <c r="B9" s="3">
+        <v>46</v>
       </c>
       <c r="C9" s="8">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="D9" s="5">
-        <v>79.976820000000004</v>
+        <v>68.439609000000004</v>
       </c>
       <c r="E9" s="3">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="F9" s="6">
         <v>75</v>
       </c>
-      <c r="G9" s="8">
-        <v>63</v>
-      </c>
+      <c r="G9" s="3"/>
       <c r="J9" s="7"/>
     </row>
     <row r="10" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="3">
-        <v>46</v>
+      <c r="B10" s="8">
+        <v>0</v>
       </c>
       <c r="C10" s="8">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="D10" s="5">
-        <v>68.439609000000004</v>
+        <v>0</v>
       </c>
       <c r="E10" s="3">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="F10" s="6">
-        <v>75</v>
-      </c>
-      <c r="G10" s="8">
-        <v>54</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G10" s="3"/>
       <c r="J10" s="7"/>
     </row>
     <row r="11" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="8">
-        <v>0</v>
+      <c r="B11" s="3">
+        <v>60</v>
       </c>
       <c r="C11" s="8">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="D11" s="5">
-        <v>0</v>
+        <v>48.463194999999999</v>
       </c>
       <c r="E11" s="3">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F11" s="6">
-        <v>0</v>
-      </c>
-      <c r="G11" s="8">
-        <v>0</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="G11" s="3"/>
       <c r="J11" s="7"/>
     </row>
     <row r="12" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -742,85 +712,78 @@
         <v>11</v>
       </c>
       <c r="B12" s="3">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="C12" s="8">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="D12" s="5">
-        <v>48.463194999999999</v>
+        <v>16.122202000000001</v>
       </c>
       <c r="E12" s="3">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F12" s="6">
-        <v>50</v>
-      </c>
-      <c r="G12" s="8">
-        <v>71</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="G12" s="3"/>
       <c r="J12" s="7"/>
     </row>
     <row r="13" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="3" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="B13" s="3">
-        <v>33</v>
-      </c>
-      <c r="C13" s="8">
+        <v>54</v>
+      </c>
+      <c r="C13" s="9">
+        <v>40</v>
+      </c>
+      <c r="D13" s="5">
+        <v>32.093606000000001</v>
+      </c>
+      <c r="E13" s="3">
         <v>28</v>
       </c>
-      <c r="D13" s="5">
-        <v>16.122202000000001</v>
-      </c>
-      <c r="E13" s="3">
-        <v>13</v>
-      </c>
       <c r="F13" s="6">
         <v>75</v>
       </c>
-      <c r="G13" s="8">
-        <v>28</v>
-      </c>
+      <c r="G13" s="3"/>
       <c r="J13" s="7"/>
     </row>
     <row r="14" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="3">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C14" s="9">
-        <v>40</v>
+        <v>77</v>
       </c>
       <c r="D14" s="5">
-        <v>32.093606000000001</v>
+        <v>100</v>
       </c>
       <c r="E14" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F14" s="6">
         <v>75</v>
-      </c>
-      <c r="G14" s="9">
-        <v>40</v>
       </c>
       <c r="J14" s="7"/>
     </row>
     <row r="15" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="3" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="B15" s="3">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C15" s="9">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="D15" s="5">
-        <v>100</v>
+        <v>98.785881000000003</v>
       </c>
       <c r="E15" s="3">
         <v>29</v>
@@ -828,68 +791,59 @@
       <c r="F15" s="6">
         <v>75</v>
       </c>
-      <c r="G15" s="9">
-        <v>77</v>
-      </c>
     </row>
     <row r="16" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="3" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="B16" s="3">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="C16" s="9">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="D16" s="5">
-        <v>98.785881000000003</v>
+        <v>33.697581</v>
       </c>
       <c r="E16" s="3">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="F16" s="6">
-        <v>75</v>
-      </c>
-      <c r="G16" s="9">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B17" s="3">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C17" s="9">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="D17" s="5">
-        <v>33.697581</v>
+        <v>27.589265999999999</v>
       </c>
       <c r="E17" s="3">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F17" s="6">
-        <v>25</v>
-      </c>
-      <c r="G17" s="9">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="3" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="B18" s="3">
         <v>42</v>
       </c>
       <c r="C18" s="9">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D18" s="5">
-        <v>27.589265999999999</v>
+        <v>7.9226970000000003</v>
       </c>
       <c r="E18" s="3">
         <v>20</v>
@@ -897,266 +851,230 @@
       <c r="F18" s="6">
         <v>50</v>
       </c>
-      <c r="G18" s="9">
+    </row>
+    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="3">
+        <v>50</v>
+      </c>
+      <c r="C19" s="9">
+        <v>31</v>
+      </c>
+      <c r="D19" s="5">
+        <v>2.0700189999999998</v>
+      </c>
+      <c r="E19" s="3">
+        <v>27</v>
+      </c>
+      <c r="F19" s="6">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="3">
+        <v>38</v>
+      </c>
+      <c r="C20" s="9">
+        <v>44</v>
+      </c>
+      <c r="D20" s="5">
+        <v>98.541549000000003</v>
+      </c>
+      <c r="E20" s="3">
+        <v>37</v>
+      </c>
+      <c r="F20" s="6">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="3" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" s="3">
-        <v>42</v>
-      </c>
-      <c r="C19" s="9">
-        <v>26</v>
-      </c>
-      <c r="D19" s="5">
-        <v>7.9226970000000003</v>
-      </c>
-      <c r="E19" s="3">
-        <v>20</v>
-      </c>
-      <c r="F19" s="6">
-        <v>50</v>
-      </c>
-      <c r="G19" s="9">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" s="3">
-        <v>50</v>
-      </c>
-      <c r="C20" s="9">
-        <v>31</v>
-      </c>
-      <c r="D20" s="5">
-        <v>2.0700189999999998</v>
-      </c>
-      <c r="E20" s="3">
-        <v>27</v>
-      </c>
-      <c r="F20" s="6">
-        <v>75</v>
-      </c>
-      <c r="G20" s="9">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="3" t="s">
+      <c r="B21" s="3">
         <v>19</v>
       </c>
-      <c r="B21" s="3">
-        <v>38</v>
-      </c>
       <c r="C21" s="9">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D21" s="5">
-        <v>98.541549000000003</v>
+        <v>96.038651999999999</v>
       </c>
       <c r="E21" s="3">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="F21" s="6">
         <v>50</v>
       </c>
-      <c r="G21" s="9">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="3" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="B22" s="3">
+        <v>66</v>
+      </c>
+      <c r="C22" s="9">
+        <v>58</v>
+      </c>
+      <c r="D22" s="5">
+        <v>96.452656000000005</v>
+      </c>
+      <c r="E22" s="3">
+        <v>28</v>
+      </c>
+      <c r="F22" s="6">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23" s="10">
+        <v>0</v>
+      </c>
+      <c r="C23" s="9">
+        <v>0</v>
+      </c>
+      <c r="D23" s="5">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3">
+        <v>0</v>
+      </c>
+      <c r="F23" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="9">
-        <v>54</v>
-      </c>
-      <c r="D22" s="5">
-        <v>96.038651999999999</v>
-      </c>
-      <c r="E22" s="3">
+      <c r="B24" s="3">
+        <v>1</v>
+      </c>
+      <c r="C24" s="9">
+        <v>3</v>
+      </c>
+      <c r="D24" s="5">
+        <v>6.4642460000000002</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B25" s="3">
+        <v>34</v>
+      </c>
+      <c r="C25" s="9">
+        <v>41</v>
+      </c>
+      <c r="D25" s="5">
+        <v>94.994204999999994</v>
+      </c>
+      <c r="E25" s="3">
+        <v>30</v>
+      </c>
+      <c r="F25" s="6">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B26" s="3">
+        <v>40</v>
+      </c>
+      <c r="C26" s="9">
+        <v>38</v>
+      </c>
+      <c r="D26" s="5">
+        <v>3.1144660000000002</v>
+      </c>
+      <c r="E26" s="10">
+        <v>67</v>
+      </c>
+      <c r="F26" s="6">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B27" s="3">
+        <v>28</v>
+      </c>
+      <c r="C27" s="9">
+        <v>29</v>
+      </c>
+      <c r="D27" s="5">
+        <v>57.335276</v>
+      </c>
+      <c r="E27" s="3">
+        <v>15</v>
+      </c>
+      <c r="F27" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" s="3">
+        <v>0</v>
+      </c>
+      <c r="C28" s="9">
+        <v>0</v>
+      </c>
+      <c r="D28" s="5">
+        <v>9.3811470000000003</v>
+      </c>
+      <c r="E28" s="10">
         <v>4</v>
       </c>
-      <c r="F22" s="6">
-        <v>50</v>
-      </c>
-      <c r="G22" s="9">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B23" s="3">
-        <v>66</v>
-      </c>
-      <c r="C23" s="9">
-        <v>58</v>
-      </c>
-      <c r="D23" s="5">
-        <v>96.452656000000005</v>
-      </c>
-      <c r="E23" s="3">
-        <v>28</v>
-      </c>
-      <c r="F23" s="6">
-        <v>75</v>
-      </c>
-      <c r="G23" s="9">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B24" s="10">
-        <v>0</v>
-      </c>
-      <c r="C24" s="9">
-        <v>0</v>
-      </c>
-      <c r="D24" s="5">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="6">
-        <v>0</v>
-      </c>
-      <c r="G24" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B25" s="3">
-        <v>1</v>
-      </c>
-      <c r="C25" s="9">
-        <v>3</v>
-      </c>
-      <c r="D25" s="5">
-        <v>6.4642460000000002</v>
-      </c>
-      <c r="E25" s="3">
-        <v>0</v>
-      </c>
-      <c r="F25" s="6">
-        <v>0</v>
-      </c>
-      <c r="G25" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B26" s="3">
-        <v>34</v>
-      </c>
-      <c r="C26" s="9">
-        <v>41</v>
-      </c>
-      <c r="D26" s="5">
-        <v>94.994204999999994</v>
-      </c>
-      <c r="E26" s="3">
-        <v>30</v>
-      </c>
-      <c r="F26" s="6">
-        <v>75</v>
-      </c>
-      <c r="G26" s="9">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="3" t="s">
+      <c r="F28" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B27" s="3">
-        <v>40</v>
-      </c>
-      <c r="C27" s="9">
-        <v>38</v>
-      </c>
-      <c r="D27" s="5">
-        <v>3.1144660000000002</v>
-      </c>
-      <c r="E27" s="10">
-        <v>67</v>
-      </c>
-      <c r="F27" s="6">
-        <v>50</v>
-      </c>
-      <c r="G27" s="9">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="3" t="s">
+      <c r="B29" s="3">
+        <v>13</v>
+      </c>
+      <c r="C29" s="9">
+        <v>7</v>
+      </c>
+      <c r="D29" s="5">
+        <v>4.3753520000000004</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="B28" s="3">
-        <v>28</v>
-      </c>
-      <c r="C28" s="9">
-        <v>29</v>
-      </c>
-      <c r="D28" s="5">
-        <v>57.335276</v>
-      </c>
-      <c r="E28" s="3">
-        <v>15</v>
-      </c>
-      <c r="F28" s="6">
-        <v>0</v>
-      </c>
-      <c r="G28" s="9">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B29" s="3">
-        <v>0</v>
-      </c>
-      <c r="C29" s="9">
-        <v>0</v>
-      </c>
-      <c r="D29" s="5">
-        <v>9.3811470000000003</v>
-      </c>
-      <c r="E29" s="10">
-        <v>4</v>
-      </c>
-      <c r="F29" s="6">
-        <v>0</v>
-      </c>
-      <c r="G29" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="3" t="s">
-        <v>27</v>
       </c>
       <c r="B30" s="3">
         <v>13</v>
@@ -1173,13 +1091,10 @@
       <c r="F30" s="6">
         <v>0</v>
       </c>
-      <c r="G30" s="9">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B31" s="3">
         <v>13</v>
@@ -1188,62 +1103,33 @@
         <v>7</v>
       </c>
       <c r="D31" s="5">
-        <v>4.3753520000000004</v>
+        <v>9.3811470000000003</v>
       </c>
       <c r="E31" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F31" s="6">
         <v>0</v>
       </c>
-      <c r="G31" s="9">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B32" s="3">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C32" s="9">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D32" s="5">
-        <v>9.3811470000000003</v>
+        <v>5.20336</v>
       </c>
       <c r="E32" s="3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F32" s="6">
         <v>0</v>
-      </c>
-      <c r="G32" s="9">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B33" s="3">
-        <v>8</v>
-      </c>
-      <c r="C33" s="9">
-        <v>9</v>
-      </c>
-      <c r="D33" s="5">
-        <v>5.20336</v>
-      </c>
-      <c r="E33" s="3">
-        <v>0</v>
-      </c>
-      <c r="F33" s="6">
-        <v>0</v>
-      </c>
-      <c r="G33" s="9">
-        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Metrics_Database.xlsx
+++ b/Data/Metrics_Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pablopadres/Documents/School/MS2/thesis/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24873022-9693-DA4D-9BB0-0D50950B494E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B5E7EE8-99D0-C54C-A115-9F568D464DA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>Brand</t>
   </si>
@@ -104,9 +104,6 @@
     <t xml:space="preserve">Marc Jacobs </t>
   </si>
   <si>
-    <t>Tom Ford Fashion</t>
-  </si>
-  <si>
     <t>Urban Outfitters</t>
   </si>
   <si>
@@ -144,13 +141,19 @@
   </si>
   <si>
     <t>Kate Spade &amp; Co.</t>
+  </si>
+  <si>
+    <t>Ethical Compliance Score</t>
+  </si>
+  <si>
+    <t>Tom Ford</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -178,25 +181,25 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="System-ui"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor rgb="FFEA9999"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -211,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -219,16 +222,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -448,7 +445,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:Z32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="24.6640625" customWidth="1"/>
     <col min="3" max="3" width="14.83203125" customWidth="1"/>
@@ -458,26 +455,28 @@
     <col min="9" max="9" width="18.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="41" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:26" ht="41" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G1" s="1"/>
+      <c r="G1" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="I1" s="1"/>
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
@@ -494,643 +493,788 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
     </row>
-    <row r="2" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:26" ht="15.75" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="6">
         <v>48</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="6">
         <v>34</v>
       </c>
-      <c r="D2" s="5">
-        <v>47.227265000000003</v>
-      </c>
-      <c r="E2" s="3">
+      <c r="D2" s="7">
+        <v>37</v>
+      </c>
+      <c r="E2" s="6">
         <v>23</v>
       </c>
       <c r="F2" s="6">
         <v>75</v>
       </c>
-      <c r="G2" s="3"/>
+      <c r="G2" s="8">
+        <f>(B2*0.3) + (C2*0.15) + (D2*0.2) + (E2*0.2) + (F2*0.15)</f>
+        <v>42.75</v>
+      </c>
+      <c r="H2" s="6"/>
       <c r="J2" s="4"/>
     </row>
-    <row r="3" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:26" ht="15.75" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="6">
         <v>48</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="6">
         <v>34</v>
       </c>
-      <c r="D3" s="5">
-        <v>47.227265000000003</v>
-      </c>
-      <c r="E3" s="3">
+      <c r="D3" s="7">
+        <v>37</v>
+      </c>
+      <c r="E3" s="6">
         <v>23</v>
       </c>
       <c r="F3" s="6">
         <v>75</v>
       </c>
-    </row>
-    <row r="4" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G3" s="8">
+        <f t="shared" ref="G3:G32" si="0">(B3*0.3) + (C3*0.15) + (D3*0.2) + (E3*0.2) + (F3*0.15)</f>
+        <v>42.75</v>
+      </c>
+      <c r="H3" s="6"/>
+    </row>
+    <row r="4" spans="1:26" ht="15.75" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="6">
         <v>48</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="6">
         <v>34</v>
       </c>
-      <c r="D4" s="5">
-        <v>52.502898000000002</v>
-      </c>
-      <c r="E4" s="3">
+      <c r="D4" s="7">
+        <v>86</v>
+      </c>
+      <c r="E4" s="6">
         <v>23</v>
       </c>
       <c r="F4" s="6">
         <v>75</v>
       </c>
-    </row>
-    <row r="5" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G4" s="8">
+        <f t="shared" si="0"/>
+        <v>52.550000000000004</v>
+      </c>
+      <c r="H4" s="6"/>
+    </row>
+    <row r="5" spans="1:26" ht="15.75" customHeight="1">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="6">
         <v>21</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="6">
         <v>47</v>
       </c>
-      <c r="D5" s="5">
-        <v>59.200969999999998</v>
-      </c>
-      <c r="E5" s="3">
+      <c r="D5" s="7">
+        <v>83</v>
+      </c>
+      <c r="E5" s="6">
         <v>28</v>
       </c>
       <c r="F5" s="6">
         <v>0</v>
       </c>
-      <c r="G5" s="3"/>
-    </row>
-    <row r="6" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G5" s="8">
+        <f t="shared" si="0"/>
+        <v>35.550000000000004</v>
+      </c>
+      <c r="H5" s="6"/>
+    </row>
+    <row r="6" spans="1:26" ht="15.75" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="6">
         <v>33</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="6">
         <v>52</v>
       </c>
-      <c r="D6" s="5">
-        <v>66.697587999999996</v>
-      </c>
-      <c r="E6" s="3">
+      <c r="D6" s="7">
+        <v>89</v>
+      </c>
+      <c r="E6" s="6">
         <v>14</v>
       </c>
       <c r="F6" s="6">
         <v>75</v>
       </c>
-      <c r="G6" s="3"/>
-    </row>
-    <row r="7" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G6" s="8">
+        <f t="shared" si="0"/>
+        <v>49.55</v>
+      </c>
+      <c r="H6" s="6"/>
+    </row>
+    <row r="7" spans="1:26" ht="15.75" customHeight="1">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="6">
         <v>50</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="6">
         <v>34</v>
       </c>
-      <c r="D7" s="5">
-        <v>30.277775999999999</v>
-      </c>
-      <c r="E7" s="3">
+      <c r="D7" s="7">
+        <v>60</v>
+      </c>
+      <c r="E7" s="6">
         <v>27</v>
       </c>
       <c r="F7" s="6">
         <v>75</v>
       </c>
-      <c r="G7" s="3"/>
-    </row>
-    <row r="8" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G7" s="8">
+        <f t="shared" si="0"/>
+        <v>48.75</v>
+      </c>
+      <c r="H7" s="6"/>
+    </row>
+    <row r="8" spans="1:26" ht="15.75" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="6">
         <v>28</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="6">
         <v>20</v>
       </c>
-      <c r="D8" s="5">
-        <v>28.913499000000002</v>
-      </c>
-      <c r="E8" s="3">
+      <c r="D8" s="7">
+        <v>70</v>
+      </c>
+      <c r="E8" s="6">
         <v>6</v>
       </c>
       <c r="F8" s="6">
         <v>50</v>
       </c>
-      <c r="G8" s="3"/>
-      <c r="J8" s="7"/>
-    </row>
-    <row r="9" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G8" s="8">
+        <f t="shared" si="0"/>
+        <v>34.099999999999994</v>
+      </c>
+      <c r="H8" s="6"/>
+      <c r="J8" s="5"/>
+    </row>
+    <row r="9" spans="1:26" ht="15.75" customHeight="1">
       <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="6">
         <v>46</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="6">
         <v>54</v>
       </c>
-      <c r="D9" s="5">
-        <v>68.439609000000004</v>
-      </c>
-      <c r="E9" s="3">
+      <c r="D9" s="7">
+        <v>70</v>
+      </c>
+      <c r="E9" s="6">
         <v>29</v>
       </c>
       <c r="F9" s="6">
         <v>75</v>
       </c>
-      <c r="G9" s="3"/>
-      <c r="J9" s="7"/>
-    </row>
-    <row r="10" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G9" s="8">
+        <f t="shared" si="0"/>
+        <v>52.95</v>
+      </c>
+      <c r="H9" s="6"/>
+      <c r="J9" s="5"/>
+    </row>
+    <row r="10" spans="1:26" ht="15.75" customHeight="1">
       <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="8">
-        <v>0</v>
-      </c>
-      <c r="C10" s="8">
-        <v>0</v>
-      </c>
-      <c r="D10" s="5">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3">
+      <c r="B10" s="6">
+        <v>0</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0</v>
+      </c>
+      <c r="D10" s="7">
+        <v>63</v>
+      </c>
+      <c r="E10" s="6">
         <v>0</v>
       </c>
       <c r="F10" s="6">
         <v>0</v>
       </c>
-      <c r="G10" s="3"/>
-      <c r="J10" s="7"/>
-    </row>
-    <row r="11" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G10" s="8">
+        <f t="shared" si="0"/>
+        <v>12.600000000000001</v>
+      </c>
+      <c r="H10" s="6"/>
+      <c r="J10" s="5"/>
+    </row>
+    <row r="11" spans="1:26" ht="15.75" customHeight="1">
       <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="6">
         <v>60</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="6">
         <v>71</v>
       </c>
-      <c r="D11" s="5">
-        <v>48.463194999999999</v>
-      </c>
-      <c r="E11" s="3">
+      <c r="D11" s="7">
+        <v>71</v>
+      </c>
+      <c r="E11" s="6">
         <v>26</v>
       </c>
       <c r="F11" s="6">
         <v>50</v>
       </c>
-      <c r="G11" s="3"/>
-      <c r="J11" s="7"/>
-    </row>
-    <row r="12" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G11" s="8">
+        <f t="shared" si="0"/>
+        <v>55.550000000000004</v>
+      </c>
+      <c r="H11" s="6"/>
+      <c r="J11" s="5"/>
+    </row>
+    <row r="12" spans="1:26" ht="15.75" customHeight="1">
       <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="6">
         <v>33</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="6">
         <v>28</v>
       </c>
-      <c r="D12" s="5">
-        <v>16.122202000000001</v>
-      </c>
-      <c r="E12" s="3">
+      <c r="D12" s="7">
+        <v>62</v>
+      </c>
+      <c r="E12" s="6">
         <v>13</v>
       </c>
       <c r="F12" s="6">
         <v>75</v>
       </c>
-      <c r="G12" s="3"/>
-      <c r="J12" s="7"/>
-    </row>
-    <row r="13" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G12" s="8">
+        <f t="shared" si="0"/>
+        <v>40.35</v>
+      </c>
+      <c r="H12" s="6"/>
+      <c r="J12" s="5"/>
+    </row>
+    <row r="13" spans="1:26" ht="15.75" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" s="3">
+        <v>34</v>
+      </c>
+      <c r="B13" s="6">
         <v>54</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C13" s="6">
         <v>40</v>
       </c>
-      <c r="D13" s="5">
-        <v>32.093606000000001</v>
-      </c>
-      <c r="E13" s="3">
+      <c r="D13" s="7">
+        <v>99</v>
+      </c>
+      <c r="E13" s="6">
         <v>28</v>
       </c>
       <c r="F13" s="6">
         <v>75</v>
       </c>
-      <c r="G13" s="3"/>
-      <c r="J13" s="7"/>
-    </row>
-    <row r="14" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G13" s="8">
+        <f t="shared" si="0"/>
+        <v>58.85</v>
+      </c>
+      <c r="H13" s="6"/>
+      <c r="J13" s="5"/>
+    </row>
+    <row r="14" spans="1:26" ht="15.75" customHeight="1">
       <c r="A14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="6">
         <v>50</v>
       </c>
-      <c r="C14" s="9">
+      <c r="C14" s="6">
         <v>77</v>
       </c>
-      <c r="D14" s="5">
-        <v>100</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="7">
+        <v>88</v>
+      </c>
+      <c r="E14" s="6">
         <v>29</v>
       </c>
       <c r="F14" s="6">
         <v>75</v>
       </c>
-      <c r="J14" s="7"/>
-    </row>
-    <row r="15" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G14" s="8">
+        <f t="shared" si="0"/>
+        <v>61.2</v>
+      </c>
+      <c r="H14" s="6"/>
+      <c r="J14" s="5"/>
+    </row>
+    <row r="15" spans="1:26" ht="15.75" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" s="3">
+        <v>33</v>
+      </c>
+      <c r="B15" s="6">
         <v>48</v>
       </c>
-      <c r="C15" s="9">
+      <c r="C15" s="6">
         <v>61</v>
       </c>
-      <c r="D15" s="5">
-        <v>98.785881000000003</v>
-      </c>
-      <c r="E15" s="3">
+      <c r="D15" s="7">
+        <v>77</v>
+      </c>
+      <c r="E15" s="6">
         <v>29</v>
       </c>
       <c r="F15" s="6">
         <v>75</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G15" s="8">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="H15" s="6"/>
+    </row>
+    <row r="16" spans="1:26" ht="15.75" customHeight="1">
       <c r="A16" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="6">
         <v>23</v>
       </c>
-      <c r="C16" s="9">
+      <c r="C16" s="6">
         <v>19</v>
       </c>
-      <c r="D16" s="5">
-        <v>33.697581</v>
-      </c>
-      <c r="E16" s="3">
+      <c r="D16" s="7">
+        <v>65</v>
+      </c>
+      <c r="E16" s="6">
         <v>13</v>
       </c>
       <c r="F16" s="6">
         <v>25</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G16" s="8">
+        <f t="shared" si="0"/>
+        <v>29.1</v>
+      </c>
+      <c r="H16" s="6"/>
+    </row>
+    <row r="17" spans="1:8" ht="15.75" customHeight="1">
       <c r="A17" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="6">
         <v>42</v>
       </c>
-      <c r="C17" s="9">
+      <c r="C17" s="6">
         <v>33</v>
       </c>
-      <c r="D17" s="5">
-        <v>27.589265999999999</v>
-      </c>
-      <c r="E17" s="3">
+      <c r="D17" s="7">
+        <v>74</v>
+      </c>
+      <c r="E17" s="6">
         <v>20</v>
       </c>
       <c r="F17" s="6">
         <v>50</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G17" s="8">
+        <f t="shared" si="0"/>
+        <v>43.85</v>
+      </c>
+      <c r="H17" s="6"/>
+    </row>
+    <row r="18" spans="1:8" ht="15.75" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B18" s="3">
+        <v>35</v>
+      </c>
+      <c r="B18" s="6">
         <v>42</v>
       </c>
-      <c r="C18" s="9">
+      <c r="C18" s="6">
         <v>26</v>
       </c>
-      <c r="D18" s="5">
-        <v>7.9226970000000003</v>
-      </c>
-      <c r="E18" s="3">
+      <c r="D18" s="7">
+        <v>86</v>
+      </c>
+      <c r="E18" s="6">
         <v>20</v>
       </c>
       <c r="F18" s="6">
         <v>50</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G18" s="8">
+        <f t="shared" si="0"/>
+        <v>45.2</v>
+      </c>
+      <c r="H18" s="6"/>
+    </row>
+    <row r="19" spans="1:8" ht="15.75" customHeight="1">
       <c r="A19" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19" s="6">
         <v>50</v>
       </c>
-      <c r="C19" s="9">
+      <c r="C19" s="6">
         <v>31</v>
       </c>
-      <c r="D19" s="5">
-        <v>2.0700189999999998</v>
-      </c>
-      <c r="E19" s="3">
+      <c r="D19" s="7">
+        <v>98</v>
+      </c>
+      <c r="E19" s="6">
         <v>27</v>
       </c>
       <c r="F19" s="6">
         <v>75</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G19" s="8">
+        <f t="shared" si="0"/>
+        <v>55.9</v>
+      </c>
+      <c r="H19" s="6"/>
+    </row>
+    <row r="20" spans="1:8" ht="15.75" customHeight="1">
       <c r="A20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20" s="6">
         <v>38</v>
       </c>
-      <c r="C20" s="9">
+      <c r="C20" s="6">
         <v>44</v>
       </c>
-      <c r="D20" s="5">
-        <v>98.541549000000003</v>
-      </c>
-      <c r="E20" s="3">
+      <c r="D20" s="7">
+        <v>97</v>
+      </c>
+      <c r="E20" s="6">
         <v>37</v>
       </c>
       <c r="F20" s="6">
         <v>50</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G20" s="8">
+        <f t="shared" si="0"/>
+        <v>52.300000000000004</v>
+      </c>
+      <c r="H20" s="6"/>
+    </row>
+    <row r="21" spans="1:8" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B21" s="3">
+        <v>32</v>
+      </c>
+      <c r="B21" s="6">
         <v>19</v>
       </c>
-      <c r="C21" s="9">
+      <c r="C21" s="6">
         <v>54</v>
       </c>
-      <c r="D21" s="5">
-        <v>96.038651999999999</v>
-      </c>
-      <c r="E21" s="3">
+      <c r="D21" s="7">
+        <v>97</v>
+      </c>
+      <c r="E21" s="6">
         <v>4</v>
       </c>
       <c r="F21" s="6">
         <v>50</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G21" s="8">
+        <f t="shared" si="0"/>
+        <v>41.5</v>
+      </c>
+      <c r="H21" s="6"/>
+    </row>
+    <row r="22" spans="1:8" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B22" s="6">
         <v>66</v>
       </c>
-      <c r="C22" s="9">
+      <c r="C22" s="6">
         <v>58</v>
       </c>
-      <c r="D22" s="5">
-        <v>96.452656000000005</v>
-      </c>
-      <c r="E22" s="3">
+      <c r="D22" s="7">
+        <v>70</v>
+      </c>
+      <c r="E22" s="6">
         <v>28</v>
       </c>
       <c r="F22" s="6">
         <v>75</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G22" s="8">
+        <f t="shared" si="0"/>
+        <v>59.35</v>
+      </c>
+      <c r="H22" s="6"/>
+    </row>
+    <row r="23" spans="1:8" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="10">
-        <v>0</v>
-      </c>
-      <c r="C23" s="9">
-        <v>0</v>
-      </c>
-      <c r="D23" s="5">
-        <v>0</v>
-      </c>
-      <c r="E23" s="3">
+      <c r="B23" s="6">
+        <v>0</v>
+      </c>
+      <c r="C23" s="6">
+        <v>0</v>
+      </c>
+      <c r="D23" s="7">
+        <v>73</v>
+      </c>
+      <c r="E23" s="6">
         <v>0</v>
       </c>
       <c r="F23" s="6">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G23" s="8">
+        <f t="shared" si="0"/>
+        <v>14.600000000000001</v>
+      </c>
+      <c r="H23" s="6"/>
+    </row>
+    <row r="24" spans="1:8" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B24" s="6">
         <v>1</v>
       </c>
-      <c r="C24" s="9">
+      <c r="C24" s="6">
         <v>3</v>
       </c>
-      <c r="D24" s="5">
-        <v>6.4642460000000002</v>
-      </c>
-      <c r="E24" s="3">
+      <c r="D24" s="7">
+        <v>96</v>
+      </c>
+      <c r="E24" s="6">
         <v>0</v>
       </c>
       <c r="F24" s="6">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G24" s="8">
+        <f t="shared" si="0"/>
+        <v>19.950000000000003</v>
+      </c>
+      <c r="H24" s="6"/>
+    </row>
+    <row r="25" spans="1:8" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B25" s="6">
         <v>34</v>
       </c>
-      <c r="C25" s="9">
+      <c r="C25" s="6">
         <v>41</v>
       </c>
-      <c r="D25" s="5">
-        <v>94.994204999999994</v>
-      </c>
-      <c r="E25" s="3">
+      <c r="D25" s="7">
+        <v>100</v>
+      </c>
+      <c r="E25" s="6">
         <v>30</v>
       </c>
       <c r="F25" s="6">
         <v>75</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G25" s="8">
+        <f t="shared" si="0"/>
+        <v>53.599999999999994</v>
+      </c>
+      <c r="H25" s="6"/>
+    </row>
+    <row r="26" spans="1:8" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B26" s="6">
         <v>40</v>
       </c>
-      <c r="C26" s="9">
+      <c r="C26" s="6">
         <v>38</v>
       </c>
-      <c r="D26" s="5">
-        <v>3.1144660000000002</v>
-      </c>
-      <c r="E26" s="10">
-        <v>67</v>
+      <c r="D26" s="7">
+        <v>86</v>
+      </c>
+      <c r="E26" s="6">
+        <v>23</v>
       </c>
       <c r="F26" s="6">
         <v>50</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G26" s="8">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="H26" s="6"/>
+    </row>
+    <row r="27" spans="1:8" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B27" s="3">
+      <c r="B27" s="6">
         <v>28</v>
       </c>
-      <c r="C27" s="9">
+      <c r="C27" s="6">
         <v>29</v>
       </c>
-      <c r="D27" s="5">
-        <v>57.335276</v>
-      </c>
-      <c r="E27" s="3">
+      <c r="D27" s="7">
+        <v>100</v>
+      </c>
+      <c r="E27" s="6">
         <v>15</v>
       </c>
       <c r="F27" s="6">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G27" s="8">
+        <f t="shared" si="0"/>
+        <v>35.75</v>
+      </c>
+      <c r="H27" s="6"/>
+    </row>
+    <row r="28" spans="1:8" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="6">
+        <v>33</v>
+      </c>
+      <c r="C28" s="6">
+        <v>0</v>
+      </c>
+      <c r="D28" s="7">
+        <v>72</v>
+      </c>
+      <c r="E28" s="6">
+        <v>18</v>
+      </c>
+      <c r="F28" s="6">
+        <v>0</v>
+      </c>
+      <c r="G28" s="8">
+        <f t="shared" si="0"/>
+        <v>27.900000000000002</v>
+      </c>
+      <c r="H28" s="6"/>
+    </row>
+    <row r="29" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A29" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B28" s="3">
-        <v>0</v>
-      </c>
-      <c r="C28" s="9">
-        <v>0</v>
-      </c>
-      <c r="D28" s="5">
-        <v>9.3811470000000003</v>
-      </c>
-      <c r="E28" s="10">
-        <v>4</v>
-      </c>
-      <c r="F28" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="3" t="s">
+      <c r="B29" s="6">
+        <v>13</v>
+      </c>
+      <c r="C29" s="6">
+        <v>7</v>
+      </c>
+      <c r="D29" s="7">
+        <v>72</v>
+      </c>
+      <c r="E29" s="6">
+        <v>0</v>
+      </c>
+      <c r="F29" s="6">
+        <v>0</v>
+      </c>
+      <c r="G29" s="8">
+        <f t="shared" si="0"/>
+        <v>19.350000000000001</v>
+      </c>
+      <c r="H29" s="6"/>
+    </row>
+    <row r="30" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A30" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B30" s="6">
         <v>13</v>
       </c>
-      <c r="C29" s="9">
+      <c r="C30" s="6">
         <v>7</v>
       </c>
-      <c r="D29" s="5">
-        <v>4.3753520000000004</v>
-      </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
-      <c r="F29" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="3" t="s">
+      <c r="D30" s="7">
+        <v>100</v>
+      </c>
+      <c r="E30" s="6">
+        <v>0</v>
+      </c>
+      <c r="F30" s="6">
+        <v>0</v>
+      </c>
+      <c r="G30" s="8">
+        <f t="shared" si="0"/>
+        <v>24.95</v>
+      </c>
+      <c r="H30" s="6"/>
+    </row>
+    <row r="31" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A31" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B31" s="6">
         <v>13</v>
       </c>
-      <c r="C30" s="9">
+      <c r="C31" s="6">
         <v>7</v>
       </c>
-      <c r="D30" s="5">
-        <v>4.3753520000000004</v>
-      </c>
-      <c r="E30" s="3">
-        <v>0</v>
-      </c>
-      <c r="F30" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="3" t="s">
+      <c r="D31" s="7">
+        <v>74</v>
+      </c>
+      <c r="E31" s="6">
+        <v>9</v>
+      </c>
+      <c r="F31" s="6">
+        <v>0</v>
+      </c>
+      <c r="G31" s="8">
+        <f t="shared" si="0"/>
+        <v>21.55</v>
+      </c>
+      <c r="H31" s="6"/>
+    </row>
+    <row r="32" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A32" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B31" s="3">
-        <v>13</v>
-      </c>
-      <c r="C31" s="9">
-        <v>7</v>
-      </c>
-      <c r="D31" s="5">
-        <v>9.3811470000000003</v>
-      </c>
-      <c r="E31" s="3">
+      <c r="B32" s="6">
+        <v>8</v>
+      </c>
+      <c r="C32" s="6">
         <v>9</v>
       </c>
-      <c r="F31" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B32" s="3">
-        <v>8</v>
-      </c>
-      <c r="C32" s="9">
-        <v>9</v>
-      </c>
-      <c r="D32" s="5">
-        <v>5.20336</v>
-      </c>
-      <c r="E32" s="3">
+      <c r="D32" s="7">
+        <v>74</v>
+      </c>
+      <c r="E32" s="6">
         <v>0</v>
       </c>
       <c r="F32" s="6">
         <v>0</v>
       </c>
+      <c r="G32" s="8">
+        <f t="shared" si="0"/>
+        <v>18.55</v>
+      </c>
+      <c r="H32" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/Metrics_Database.xlsx
+++ b/Data/Metrics_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pablopadres/Documents/School/MS2/thesis/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B5E7EE8-99D0-C54C-A115-9F568D464DA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{430FB275-3E51-A643-814F-3CD8D7939C80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11900" yWindow="760" windowWidth="18340" windowHeight="17740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ethical Metrics Database" sheetId="3" r:id="rId1"/>
@@ -153,7 +153,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -188,11 +188,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="System-ui"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -214,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -224,7 +219,6 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -445,7 +439,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:Z32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="24.6640625" customWidth="1"/>
     <col min="3" max="3" width="14.83203125" customWidth="1"/>
@@ -455,7 +449,7 @@
     <col min="9" max="9" width="18.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="41" customHeight="1">
+    <row r="1" spans="1:26" ht="41" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -493,786 +487,786 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
     </row>
-    <row r="2" spans="1:26" ht="15.75" customHeight="1">
+    <row r="2" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="7">
         <v>48</v>
       </c>
-      <c r="C2" s="6">
-        <v>34</v>
+      <c r="C2" s="7">
+        <v>41.68</v>
       </c>
       <c r="D2" s="7">
         <v>37</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="7">
         <v>23</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="7">
         <v>75</v>
       </c>
-      <c r="G2" s="8">
+      <c r="G2" s="7">
         <f>(B2*0.3) + (C2*0.15) + (D2*0.2) + (E2*0.2) + (F2*0.15)</f>
-        <v>42.75</v>
+        <v>43.902000000000001</v>
       </c>
       <c r="H2" s="6"/>
       <c r="J2" s="4"/>
     </row>
-    <row r="3" spans="1:26" ht="15.75" customHeight="1">
+    <row r="3" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="7">
         <v>48</v>
       </c>
-      <c r="C3" s="6">
-        <v>34</v>
+      <c r="C3" s="7">
+        <v>41.68</v>
       </c>
       <c r="D3" s="7">
         <v>37</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="7">
         <v>23</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="7">
         <v>75</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G3" s="7">
         <f t="shared" ref="G3:G32" si="0">(B3*0.3) + (C3*0.15) + (D3*0.2) + (E3*0.2) + (F3*0.15)</f>
-        <v>42.75</v>
+        <v>43.902000000000001</v>
       </c>
       <c r="H3" s="6"/>
     </row>
-    <row r="4" spans="1:26" ht="15.75" customHeight="1">
+    <row r="4" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="7">
         <v>48</v>
       </c>
-      <c r="C4" s="6">
-        <v>34</v>
+      <c r="C4" s="7">
+        <v>41.68</v>
       </c>
       <c r="D4" s="7">
         <v>86</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="7">
         <v>23</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="7">
         <v>75</v>
       </c>
-      <c r="G4" s="8">
-        <f t="shared" si="0"/>
-        <v>52.550000000000004</v>
+      <c r="G4" s="7">
+        <f t="shared" si="0"/>
+        <v>53.701999999999998</v>
       </c>
       <c r="H4" s="6"/>
     </row>
-    <row r="5" spans="1:26" ht="15.75" customHeight="1">
+    <row r="5" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="7">
         <v>21</v>
       </c>
-      <c r="C5" s="6">
-        <v>47</v>
+      <c r="C5" s="7">
+        <v>24.92</v>
       </c>
       <c r="D5" s="7">
         <v>83</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="7">
         <v>28</v>
       </c>
-      <c r="F5" s="6">
-        <v>0</v>
-      </c>
-      <c r="G5" s="8">
-        <f t="shared" si="0"/>
-        <v>35.550000000000004</v>
+      <c r="F5" s="7">
+        <v>0</v>
+      </c>
+      <c r="G5" s="7">
+        <f t="shared" si="0"/>
+        <v>32.238</v>
       </c>
       <c r="H5" s="6"/>
     </row>
-    <row r="6" spans="1:26" ht="15.75" customHeight="1">
+    <row r="6" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <v>33</v>
       </c>
-      <c r="C6" s="6">
-        <v>52</v>
+      <c r="C6" s="7">
+        <v>40.619999999999997</v>
       </c>
       <c r="D6" s="7">
         <v>89</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="7">
         <v>14</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="7">
         <v>75</v>
       </c>
-      <c r="G6" s="8">
-        <f t="shared" si="0"/>
-        <v>49.55</v>
+      <c r="G6" s="7">
+        <f t="shared" si="0"/>
+        <v>47.842999999999996</v>
       </c>
       <c r="H6" s="6"/>
     </row>
-    <row r="7" spans="1:26" ht="15.75" customHeight="1">
+    <row r="7" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="7">
         <v>50</v>
       </c>
-      <c r="C7" s="6">
-        <v>34</v>
+      <c r="C7" s="7">
+        <v>51.55</v>
       </c>
       <c r="D7" s="7">
         <v>60</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="7">
         <v>27</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="7">
         <v>75</v>
       </c>
-      <c r="G7" s="8">
-        <f t="shared" si="0"/>
-        <v>48.75</v>
+      <c r="G7" s="7">
+        <f t="shared" si="0"/>
+        <v>51.3825</v>
       </c>
       <c r="H7" s="6"/>
     </row>
-    <row r="8" spans="1:26" ht="15.75" customHeight="1">
+    <row r="8" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="7">
         <v>28</v>
       </c>
-      <c r="C8" s="6">
-        <v>20</v>
+      <c r="C8" s="7">
+        <v>49.98</v>
       </c>
       <c r="D8" s="7">
         <v>70</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="7">
         <v>6</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="7">
         <v>50</v>
       </c>
-      <c r="G8" s="8">
-        <f t="shared" si="0"/>
-        <v>34.099999999999994</v>
+      <c r="G8" s="7">
+        <f t="shared" si="0"/>
+        <v>38.596999999999994</v>
       </c>
       <c r="H8" s="6"/>
       <c r="J8" s="5"/>
     </row>
-    <row r="9" spans="1:26" ht="15.75" customHeight="1">
+    <row r="9" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="7">
         <v>46</v>
       </c>
-      <c r="C9" s="6">
-        <v>54</v>
+      <c r="C9" s="7">
+        <v>45.71</v>
       </c>
       <c r="D9" s="7">
         <v>70</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="7">
         <v>29</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="7">
         <v>75</v>
       </c>
-      <c r="G9" s="8">
-        <f t="shared" si="0"/>
-        <v>52.95</v>
+      <c r="G9" s="7">
+        <f t="shared" si="0"/>
+        <v>51.706499999999991</v>
       </c>
       <c r="H9" s="6"/>
       <c r="J9" s="5"/>
     </row>
-    <row r="10" spans="1:26" ht="15.75" customHeight="1">
+    <row r="10" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="6">
-        <v>0</v>
-      </c>
-      <c r="C10" s="6">
-        <v>0</v>
+      <c r="B10" s="7">
+        <v>0</v>
+      </c>
+      <c r="C10" s="7">
+        <v>24.92</v>
       </c>
       <c r="D10" s="7">
         <v>63</v>
       </c>
-      <c r="E10" s="6">
-        <v>0</v>
-      </c>
-      <c r="F10" s="6">
-        <v>0</v>
-      </c>
-      <c r="G10" s="8">
-        <f t="shared" si="0"/>
-        <v>12.600000000000001</v>
+      <c r="E10" s="7">
+        <v>0</v>
+      </c>
+      <c r="F10" s="7">
+        <v>0</v>
+      </c>
+      <c r="G10" s="7">
+        <f t="shared" si="0"/>
+        <v>16.338000000000001</v>
       </c>
       <c r="H10" s="6"/>
       <c r="J10" s="5"/>
     </row>
-    <row r="11" spans="1:26" ht="15.75" customHeight="1">
+    <row r="11" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="7">
         <v>60</v>
       </c>
-      <c r="C11" s="6">
-        <v>71</v>
+      <c r="C11" s="7">
+        <v>24.92</v>
       </c>
       <c r="D11" s="7">
         <v>71</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="7">
         <v>26</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="7">
         <v>50</v>
       </c>
-      <c r="G11" s="8">
-        <f t="shared" si="0"/>
-        <v>55.550000000000004</v>
+      <c r="G11" s="7">
+        <f t="shared" si="0"/>
+        <v>48.638000000000005</v>
       </c>
       <c r="H11" s="6"/>
       <c r="J11" s="5"/>
     </row>
-    <row r="12" spans="1:26" ht="15.75" customHeight="1">
+    <row r="12" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="7">
         <v>33</v>
       </c>
-      <c r="C12" s="6">
-        <v>28</v>
+      <c r="C12" s="7">
+        <v>50.3</v>
       </c>
       <c r="D12" s="7">
         <v>62</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="7">
         <v>13</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="7">
         <v>75</v>
       </c>
-      <c r="G12" s="8">
-        <f t="shared" si="0"/>
-        <v>40.35</v>
+      <c r="G12" s="7">
+        <f t="shared" si="0"/>
+        <v>43.695</v>
       </c>
       <c r="H12" s="6"/>
       <c r="J12" s="5"/>
     </row>
-    <row r="13" spans="1:26" ht="15.75" customHeight="1">
+    <row r="13" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="7">
         <v>54</v>
       </c>
-      <c r="C13" s="6">
-        <v>40</v>
+      <c r="C13" s="7">
+        <v>65.59</v>
       </c>
       <c r="D13" s="7">
         <v>99</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="7">
         <v>28</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="7">
         <v>75</v>
       </c>
-      <c r="G13" s="8">
-        <f t="shared" si="0"/>
-        <v>58.85</v>
+      <c r="G13" s="7">
+        <f t="shared" si="0"/>
+        <v>62.688499999999998</v>
       </c>
       <c r="H13" s="6"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="14" spans="1:26" ht="15.75" customHeight="1">
+    <row r="14" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="7">
         <v>50</v>
       </c>
-      <c r="C14" s="6">
-        <v>77</v>
+      <c r="C14" s="7">
+        <v>52.34</v>
       </c>
       <c r="D14" s="7">
         <v>88</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="7">
         <v>29</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="7">
         <v>75</v>
       </c>
-      <c r="G14" s="8">
-        <f t="shared" si="0"/>
-        <v>61.2</v>
+      <c r="G14" s="7">
+        <f t="shared" si="0"/>
+        <v>57.501000000000005</v>
       </c>
       <c r="H14" s="6"/>
       <c r="J14" s="5"/>
     </row>
-    <row r="15" spans="1:26" ht="15.75" customHeight="1">
+    <row r="15" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="7">
         <v>48</v>
       </c>
-      <c r="C15" s="6">
-        <v>61</v>
+      <c r="C15" s="7">
+        <v>52.34</v>
       </c>
       <c r="D15" s="7">
         <v>77</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="7">
         <v>29</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="7">
         <v>75</v>
       </c>
-      <c r="G15" s="8">
-        <f t="shared" si="0"/>
-        <v>56</v>
+      <c r="G15" s="7">
+        <f t="shared" si="0"/>
+        <v>54.700999999999993</v>
       </c>
       <c r="H15" s="6"/>
     </row>
-    <row r="16" spans="1:26" ht="15.75" customHeight="1">
+    <row r="16" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" s="7">
         <v>23</v>
       </c>
-      <c r="C16" s="6">
-        <v>19</v>
+      <c r="C16" s="7">
+        <v>24.92</v>
       </c>
       <c r="D16" s="7">
         <v>65</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="7">
         <v>13</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16" s="7">
         <v>25</v>
       </c>
-      <c r="G16" s="8">
-        <f t="shared" si="0"/>
-        <v>29.1</v>
+      <c r="G16" s="7">
+        <f t="shared" si="0"/>
+        <v>29.988</v>
       </c>
       <c r="H16" s="6"/>
     </row>
-    <row r="17" spans="1:8" ht="15.75" customHeight="1">
+    <row r="17" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="7">
         <v>42</v>
       </c>
-      <c r="C17" s="6">
-        <v>33</v>
+      <c r="C17" s="7">
+        <v>51.11</v>
       </c>
       <c r="D17" s="7">
         <v>74</v>
       </c>
-      <c r="E17" s="6">
+      <c r="E17" s="7">
         <v>20</v>
       </c>
-      <c r="F17" s="6">
+      <c r="F17" s="7">
         <v>50</v>
       </c>
-      <c r="G17" s="8">
-        <f t="shared" si="0"/>
-        <v>43.85</v>
+      <c r="G17" s="7">
+        <f t="shared" si="0"/>
+        <v>46.566500000000005</v>
       </c>
       <c r="H17" s="6"/>
     </row>
-    <row r="18" spans="1:8" ht="15.75" customHeight="1">
+    <row r="18" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="6">
+      <c r="B18" s="7">
         <v>42</v>
       </c>
-      <c r="C18" s="6">
-        <v>26</v>
+      <c r="C18" s="7">
+        <v>51.11</v>
       </c>
       <c r="D18" s="7">
         <v>86</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E18" s="7">
         <v>20</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F18" s="7">
         <v>50</v>
       </c>
-      <c r="G18" s="8">
-        <f t="shared" si="0"/>
-        <v>45.2</v>
+      <c r="G18" s="7">
+        <f t="shared" si="0"/>
+        <v>48.966499999999996</v>
       </c>
       <c r="H18" s="6"/>
     </row>
-    <row r="19" spans="1:8" ht="15.75" customHeight="1">
+    <row r="19" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B19" s="6">
+      <c r="B19" s="7">
         <v>50</v>
       </c>
-      <c r="C19" s="6">
-        <v>31</v>
+      <c r="C19" s="7">
+        <v>51.55</v>
       </c>
       <c r="D19" s="7">
         <v>98</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E19" s="7">
         <v>27</v>
       </c>
-      <c r="F19" s="6">
+      <c r="F19" s="7">
         <v>75</v>
       </c>
-      <c r="G19" s="8">
-        <f t="shared" si="0"/>
-        <v>55.9</v>
+      <c r="G19" s="7">
+        <f t="shared" si="0"/>
+        <v>58.982499999999995</v>
       </c>
       <c r="H19" s="6"/>
     </row>
-    <row r="20" spans="1:8" ht="15.75" customHeight="1">
+    <row r="20" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B20" s="6">
+      <c r="B20" s="7">
         <v>38</v>
       </c>
-      <c r="C20" s="6">
-        <v>44</v>
+      <c r="C20" s="7">
+        <v>48.22</v>
       </c>
       <c r="D20" s="7">
         <v>97</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E20" s="7">
         <v>37</v>
       </c>
-      <c r="F20" s="6">
+      <c r="F20" s="7">
         <v>50</v>
       </c>
-      <c r="G20" s="8">
-        <f t="shared" si="0"/>
-        <v>52.300000000000004</v>
+      <c r="G20" s="7">
+        <f t="shared" si="0"/>
+        <v>52.933</v>
       </c>
       <c r="H20" s="6"/>
     </row>
-    <row r="21" spans="1:8" ht="15.75" customHeight="1">
+    <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="6">
+      <c r="B21" s="7">
         <v>19</v>
       </c>
-      <c r="C21" s="6">
-        <v>54</v>
+      <c r="C21" s="7">
+        <v>32.61</v>
       </c>
       <c r="D21" s="7">
         <v>97</v>
       </c>
-      <c r="E21" s="6">
+      <c r="E21" s="7">
         <v>4</v>
       </c>
-      <c r="F21" s="6">
+      <c r="F21" s="7">
         <v>50</v>
       </c>
-      <c r="G21" s="8">
-        <f t="shared" si="0"/>
-        <v>41.5</v>
+      <c r="G21" s="7">
+        <f t="shared" si="0"/>
+        <v>38.291499999999999</v>
       </c>
       <c r="H21" s="6"/>
     </row>
-    <row r="22" spans="1:8" ht="15.75" customHeight="1">
+    <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="6">
+      <c r="B22" s="7">
         <v>66</v>
       </c>
-      <c r="C22" s="6">
-        <v>58</v>
+      <c r="C22" s="7">
+        <v>51.89</v>
       </c>
       <c r="D22" s="7">
         <v>70</v>
       </c>
-      <c r="E22" s="6">
+      <c r="E22" s="7">
         <v>28</v>
       </c>
-      <c r="F22" s="6">
+      <c r="F22" s="7">
         <v>75</v>
       </c>
-      <c r="G22" s="8">
-        <f t="shared" si="0"/>
-        <v>59.35</v>
+      <c r="G22" s="7">
+        <f t="shared" si="0"/>
+        <v>58.433500000000002</v>
       </c>
       <c r="H22" s="6"/>
     </row>
-    <row r="23" spans="1:8" ht="15.75" customHeight="1">
+    <row r="23" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="6">
-        <v>0</v>
-      </c>
-      <c r="C23" s="6">
-        <v>0</v>
+      <c r="B23" s="7">
+        <v>0</v>
+      </c>
+      <c r="C23" s="7">
+        <v>24.92</v>
       </c>
       <c r="D23" s="7">
         <v>73</v>
       </c>
-      <c r="E23" s="6">
-        <v>0</v>
-      </c>
-      <c r="F23" s="6">
-        <v>0</v>
-      </c>
-      <c r="G23" s="8">
-        <f t="shared" si="0"/>
-        <v>14.600000000000001</v>
+      <c r="E23" s="7">
+        <v>0</v>
+      </c>
+      <c r="F23" s="7">
+        <v>0</v>
+      </c>
+      <c r="G23" s="7">
+        <f t="shared" si="0"/>
+        <v>18.338000000000001</v>
       </c>
       <c r="H23" s="6"/>
     </row>
-    <row r="24" spans="1:8" ht="15.75" customHeight="1">
+    <row r="24" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="6">
+      <c r="B24" s="7">
         <v>1</v>
       </c>
-      <c r="C24" s="6">
-        <v>3</v>
+      <c r="C24" s="7">
+        <v>24.92</v>
       </c>
       <c r="D24" s="7">
         <v>96</v>
       </c>
-      <c r="E24" s="6">
-        <v>0</v>
-      </c>
-      <c r="F24" s="6">
-        <v>0</v>
-      </c>
-      <c r="G24" s="8">
-        <f t="shared" si="0"/>
-        <v>19.950000000000003</v>
+      <c r="E24" s="7">
+        <v>0</v>
+      </c>
+      <c r="F24" s="7">
+        <v>0</v>
+      </c>
+      <c r="G24" s="7">
+        <f t="shared" si="0"/>
+        <v>23.238000000000003</v>
       </c>
       <c r="H24" s="6"/>
     </row>
-    <row r="25" spans="1:8" ht="15.75" customHeight="1">
+    <row r="25" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B25" s="6">
+      <c r="B25" s="7">
         <v>34</v>
       </c>
-      <c r="C25" s="6">
-        <v>41</v>
+      <c r="C25" s="7">
+        <v>47.2</v>
       </c>
       <c r="D25" s="7">
         <v>100</v>
       </c>
-      <c r="E25" s="6">
+      <c r="E25" s="7">
         <v>30</v>
       </c>
-      <c r="F25" s="6">
+      <c r="F25" s="7">
         <v>75</v>
       </c>
-      <c r="G25" s="8">
-        <f t="shared" si="0"/>
-        <v>53.599999999999994</v>
+      <c r="G25" s="7">
+        <f t="shared" si="0"/>
+        <v>54.53</v>
       </c>
       <c r="H25" s="6"/>
     </row>
-    <row r="26" spans="1:8" ht="15.75" customHeight="1">
+    <row r="26" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B26" s="6">
+      <c r="B26" s="7">
         <v>40</v>
       </c>
-      <c r="C26" s="6">
-        <v>38</v>
+      <c r="C26" s="7">
+        <v>47.1</v>
       </c>
       <c r="D26" s="7">
         <v>86</v>
       </c>
-      <c r="E26" s="6">
+      <c r="E26" s="7">
         <v>23</v>
       </c>
-      <c r="F26" s="6">
+      <c r="F26" s="7">
         <v>50</v>
       </c>
-      <c r="G26" s="8">
-        <f t="shared" si="0"/>
-        <v>47</v>
+      <c r="G26" s="7">
+        <f t="shared" si="0"/>
+        <v>48.365000000000002</v>
       </c>
       <c r="H26" s="6"/>
     </row>
-    <row r="27" spans="1:8" ht="15.75" customHeight="1">
+    <row r="27" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B27" s="6">
+      <c r="B27" s="7">
         <v>28</v>
       </c>
-      <c r="C27" s="6">
-        <v>29</v>
+      <c r="C27" s="7">
+        <v>24.92</v>
       </c>
       <c r="D27" s="7">
         <v>100</v>
       </c>
-      <c r="E27" s="6">
+      <c r="E27" s="7">
         <v>15</v>
       </c>
-      <c r="F27" s="6">
-        <v>0</v>
-      </c>
-      <c r="G27" s="8">
-        <f t="shared" si="0"/>
-        <v>35.75</v>
+      <c r="F27" s="7">
+        <v>0</v>
+      </c>
+      <c r="G27" s="7">
+        <f t="shared" si="0"/>
+        <v>35.137999999999998</v>
       </c>
       <c r="H27" s="6"/>
     </row>
-    <row r="28" spans="1:8" ht="15.75" customHeight="1">
+    <row r="28" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="6">
+      <c r="B28" s="7">
         <v>33</v>
       </c>
-      <c r="C28" s="6">
-        <v>0</v>
+      <c r="C28" s="7">
+        <v>98.09</v>
       </c>
       <c r="D28" s="7">
         <v>72</v>
       </c>
-      <c r="E28" s="6">
+      <c r="E28" s="7">
         <v>18</v>
       </c>
-      <c r="F28" s="6">
-        <v>0</v>
-      </c>
-      <c r="G28" s="8">
-        <f t="shared" si="0"/>
-        <v>27.900000000000002</v>
+      <c r="F28" s="7">
+        <v>0</v>
+      </c>
+      <c r="G28" s="7">
+        <f t="shared" si="0"/>
+        <v>42.613500000000002</v>
       </c>
       <c r="H28" s="6"/>
     </row>
-    <row r="29" spans="1:8" ht="15.75" customHeight="1">
+    <row r="29" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B29" s="6">
+      <c r="B29" s="7">
         <v>13</v>
       </c>
-      <c r="C29" s="6">
-        <v>7</v>
+      <c r="C29" s="7">
+        <v>24.92</v>
       </c>
       <c r="D29" s="7">
         <v>72</v>
       </c>
-      <c r="E29" s="6">
-        <v>0</v>
-      </c>
-      <c r="F29" s="6">
-        <v>0</v>
-      </c>
-      <c r="G29" s="8">
-        <f t="shared" si="0"/>
-        <v>19.350000000000001</v>
+      <c r="E29" s="7">
+        <v>0</v>
+      </c>
+      <c r="F29" s="7">
+        <v>0</v>
+      </c>
+      <c r="G29" s="7">
+        <f t="shared" si="0"/>
+        <v>22.038</v>
       </c>
       <c r="H29" s="6"/>
     </row>
-    <row r="30" spans="1:8" ht="15.75" customHeight="1">
+    <row r="30" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B30" s="6">
+      <c r="B30" s="7">
         <v>13</v>
       </c>
-      <c r="C30" s="6">
-        <v>7</v>
+      <c r="C30" s="7">
+        <v>24.92</v>
       </c>
       <c r="D30" s="7">
         <v>100</v>
       </c>
-      <c r="E30" s="6">
-        <v>0</v>
-      </c>
-      <c r="F30" s="6">
-        <v>0</v>
-      </c>
-      <c r="G30" s="8">
-        <f t="shared" si="0"/>
-        <v>24.95</v>
+      <c r="E30" s="7">
+        <v>0</v>
+      </c>
+      <c r="F30" s="7">
+        <v>0</v>
+      </c>
+      <c r="G30" s="7">
+        <f t="shared" si="0"/>
+        <v>27.637999999999998</v>
       </c>
       <c r="H30" s="6"/>
     </row>
-    <row r="31" spans="1:8" ht="15.75" customHeight="1">
+    <row r="31" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B31" s="6">
+      <c r="B31" s="7">
         <v>13</v>
       </c>
-      <c r="C31" s="6">
-        <v>7</v>
+      <c r="C31" s="7">
+        <v>24.92</v>
       </c>
       <c r="D31" s="7">
         <v>74</v>
       </c>
-      <c r="E31" s="6">
+      <c r="E31" s="7">
         <v>9</v>
       </c>
-      <c r="F31" s="6">
-        <v>0</v>
-      </c>
-      <c r="G31" s="8">
-        <f t="shared" si="0"/>
-        <v>21.55</v>
+      <c r="F31" s="7">
+        <v>0</v>
+      </c>
+      <c r="G31" s="7">
+        <f t="shared" si="0"/>
+        <v>24.238000000000003</v>
       </c>
       <c r="H31" s="6"/>
     </row>
-    <row r="32" spans="1:8" ht="15.75" customHeight="1">
+    <row r="32" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B32" s="6">
+      <c r="B32" s="7">
         <v>8</v>
       </c>
-      <c r="C32" s="6">
-        <v>9</v>
+      <c r="C32" s="7">
+        <v>24.92</v>
       </c>
       <c r="D32" s="7">
         <v>74</v>
       </c>
-      <c r="E32" s="6">
-        <v>0</v>
-      </c>
-      <c r="F32" s="6">
-        <v>0</v>
-      </c>
-      <c r="G32" s="8">
-        <f t="shared" si="0"/>
-        <v>18.55</v>
+      <c r="E32" s="7">
+        <v>0</v>
+      </c>
+      <c r="F32" s="7">
+        <v>0</v>
+      </c>
+      <c r="G32" s="7">
+        <f t="shared" si="0"/>
+        <v>20.938000000000002</v>
       </c>
       <c r="H32" s="6"/>
     </row>
